--- a/selenium-tests/StainScope_Backend_API_Test_Report.xlsx
+++ b/selenium-tests/StainScope_Backend_API_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="149">
   <si>
     <t>⚡ StainScope Backend REST API &amp; DB Validation Report</t>
   </si>
@@ -68,7 +68,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-08-21T09:22:59.823Z</t>
+    <t>2026-08-21T09:28:00.234Z</t>
   </si>
   <si>
     <t>API-TC002</t>
@@ -86,7 +86,7 @@
     <t>OpenAPI 3.0 schema validated successfully</t>
   </si>
   <si>
-    <t>2026-08-21T09:22:59.824Z</t>
+    <t>2026-08-21T09:28:00.235Z</t>
   </si>
   <si>
     <t>API-TC003</t>
@@ -198,9 +198,6 @@
   </si>
   <si>
     <t>Profile updated successfully in MySQL</t>
-  </si>
-  <si>
-    <t>2026-08-21T09:22:59.825Z</t>
   </si>
   <si>
     <t>API-TC012</t>
@@ -1246,490 +1243,490 @@
         <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>62</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" t="s">
         <v>66</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>67</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>68</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>69</v>
       </c>
-      <c r="E14" t="s">
-        <v>70</v>
-      </c>
       <c r="F14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
         <v>71</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
         <v>72</v>
       </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>73</v>
       </c>
-      <c r="E15" t="s">
-        <v>74</v>
-      </c>
       <c r="F15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" t="s">
         <v>75</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
         <v>76</v>
       </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>77</v>
       </c>
-      <c r="E16" t="s">
-        <v>78</v>
-      </c>
       <c r="F16" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
         <v>79</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
         <v>80</v>
       </c>
-      <c r="C17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>81</v>
       </c>
-      <c r="E17" t="s">
-        <v>82</v>
-      </c>
       <c r="F17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" t="s">
         <v>83</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
         <v>84</v>
       </c>
-      <c r="C18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>85</v>
       </c>
-      <c r="E18" t="s">
-        <v>86</v>
-      </c>
       <c r="F18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
         <v>87</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" t="s">
         <v>88</v>
       </c>
-      <c r="C19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>89</v>
       </c>
-      <c r="E19" t="s">
-        <v>90</v>
-      </c>
       <c r="F19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
         <v>91</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
         <v>92</v>
       </c>
-      <c r="C20" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>93</v>
       </c>
-      <c r="E20" t="s">
-        <v>94</v>
-      </c>
       <c r="F20" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" t="s">
         <v>95</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" t="s">
         <v>96</v>
       </c>
-      <c r="C21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>97</v>
       </c>
-      <c r="E21" t="s">
-        <v>98</v>
-      </c>
       <c r="F21" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
         <v>99</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>100</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>101</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>102</v>
       </c>
-      <c r="E22" t="s">
-        <v>103</v>
-      </c>
       <c r="F22" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" t="s">
         <v>104</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" t="s">
         <v>105</v>
       </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>106</v>
       </c>
-      <c r="E23" t="s">
-        <v>107</v>
-      </c>
       <c r="F23" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" t="s">
         <v>108</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" t="s">
         <v>109</v>
       </c>
-      <c r="C24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>110</v>
       </c>
-      <c r="E24" t="s">
-        <v>111</v>
-      </c>
       <c r="F24" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" t="s">
         <v>112</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
         <v>113</v>
       </c>
-      <c r="C25" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>114</v>
       </c>
-      <c r="E25" t="s">
-        <v>115</v>
-      </c>
       <c r="F25" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" t="s">
         <v>116</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" t="s">
         <v>117</v>
       </c>
-      <c r="C26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>118</v>
       </c>
-      <c r="E26" t="s">
-        <v>119</v>
-      </c>
       <c r="F26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" t="s">
         <v>120</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>121</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>122</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>123</v>
       </c>
-      <c r="E27" t="s">
-        <v>124</v>
-      </c>
       <c r="F27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" t="s">
         <v>125</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" t="s">
         <v>126</v>
       </c>
-      <c r="C28" t="s">
-        <v>122</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>127</v>
       </c>
-      <c r="E28" t="s">
-        <v>128</v>
-      </c>
       <c r="F28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" t="s">
         <v>129</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" t="s">
         <v>130</v>
       </c>
-      <c r="C29" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>131</v>
       </c>
-      <c r="E29" t="s">
-        <v>132</v>
-      </c>
       <c r="F29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" t="s">
         <v>133</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" t="s">
         <v>134</v>
       </c>
-      <c r="C30" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>135</v>
       </c>
-      <c r="E30" t="s">
-        <v>136</v>
-      </c>
       <c r="F30" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>136</v>
+      </c>
+      <c r="B31" t="s">
         <v>137</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>138</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>139</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>140</v>
       </c>
-      <c r="E31" t="s">
-        <v>141</v>
-      </c>
       <c r="F31" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" t="s">
         <v>142</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" t="s">
         <v>143</v>
       </c>
-      <c r="C32" t="s">
-        <v>139</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>144</v>
       </c>
-      <c r="E32" t="s">
-        <v>145</v>
-      </c>
       <c r="F32" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" t="s">
         <v>146</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" t="s">
         <v>147</v>
       </c>
-      <c r="C33" t="s">
-        <v>139</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>148</v>
       </c>
-      <c r="E33" t="s">
-        <v>149</v>
-      </c>
       <c r="F33" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
